--- a/entregables/Calendario-Isoval-Ago-Sep-2026.xlsx
+++ b/entregables/Calendario-Isoval-Ago-Sep-2026.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Guía rápida" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ideas de Stories" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía rápida" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideas de Stories" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario'!$A$1:$N$12</definedName>
@@ -50,18 +50,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B8131F"/>
+      <color rgb="001F5F69"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00231C10"/>
+      <color rgb="001B1E1F"/>
       <sz val="22"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00E8192C"/>
+      <color rgb="002B7D89"/>
       <sz val="11"/>
     </font>
     <font>
@@ -119,7 +119,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00231C10"/>
+        <fgColor rgb="001B1E1F"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,7 +139,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005C4A36"/>
+        <fgColor rgb="004A4F50"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,37 +159,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EDE0"/>
+        <fgColor rgb="00F5F3EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9F5EE"/>
+        <fgColor rgb="00FAF9F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBE2CF"/>
+        <fgColor rgb="00EDEAE2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E2416"/>
+        <fgColor rgb="002C3132"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009C866E"/>
+        <fgColor rgb="008A8F90"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8192C"/>
+        <fgColor rgb="002B7D89"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B8131F"/>
+        <fgColor rgb="001F5F69"/>
       </patternFill>
     </fill>
   </fills>
@@ -761,7 +761,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E8192C"/>
+    <tabColor rgb="002B7D89"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -949,12 +949,12 @@
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Crema (fondo)</t>
+          <t>Hueso (fondo)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>#F3EDE0</t>
+          <t>#F5F3EE</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
@@ -967,30 +967,30 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Crema tarjeta</t>
+          <t>Hueso tarjeta</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>#F9F5EE</t>
+          <t>#FAF9F6</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr"/>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Tarjetas y bloques dentro de un fondo crema.</t>
+          <t>Tarjetas y bloques dentro de un fondo hueso.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Crema oscuro</t>
+          <t>Hueso oscuro</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>#EBE2CF</t>
+          <t>#EDEAE2</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Carbón cálido</t>
+          <t>Ink</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>#231C10</t>
+          <t>#1B1E1F</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -1021,12 +1021,12 @@
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Carbón secciones</t>
+          <t>Ink secciones</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>#2E2416</t>
+          <t>#2C3132</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>#5C4A36</t>
+          <t>#4A4F50</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>#9C866E</t>
+          <t>#8A8F90</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr"/>
@@ -1075,43 +1075,43 @@
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Rojo Isoval</t>
+          <t>Teal Isoval</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>#E8192C</t>
+          <t>#2B7D89</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Acento del logo. Solo CTA, subrayados y viñetas.</t>
+          <t>Acento de marca. Solo CTA, subrayados, viñetas y rótulos.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Rojo profundo</t>
+          <t>Teal profundo</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>#B8131F</t>
+          <t>#1F5F69</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Estados presionados y bordes del acento.</t>
+          <t>Bordes del acento y estados presionados.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>Regla de oro: el rojo nunca pasa del 10% de la pieza. Es acento, no fondo. Los hex salen directo del sitio web, así que feed y web se ven de la misma marca.</t>
+          <t>Regla de oro: el teal nunca pasa del 10% de la pieza. Es acento, no fondo. Los tres hex base (hueso #F5F3EE / teal #2B7D89 / ink #1B1E1F) son los del manual de marca de ISOVAL; el resto son derivados para dar jerarquía.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       <c r="D30" s="27" t="n"/>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Logo en su versión a color sobre crema #F3EDE0. Es la combinación por defecto.</t>
+          <t>Logo en su versión a color sobre hueso #F5F3EE. Es la combinación por defecto.</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="D31" s="27" t="n"/>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Versión en crema o blanco sobre carbón #231C10. No poner el logo a color sobre carbón.</t>
+          <t>Versión en hueso o blanco sobre ink #1B1E1F. No poner el logo a color sobre ink.</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       <c r="D41" s="27" t="n"/>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Mínimo 3 días con stories por semana. La hoja «Ideas de Stories» trae 12 listas para usar.</t>
+          <t>Mínimo 3 días con stories por semana. Hay 12 ideas listas para usar.</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       <c r="D65" s="27" t="n"/>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Se usa «Isoval — Arquitectura &amp; Construcción» y @isoval.arq, tomado del perfil del asistente de WhatsApp. Ojo: el sitio y el logo del repositorio están a nombre de LAB A+A. Si la cuenta de Instagram ya opera como LAB A+A, cambia el nombre en los copys.</t>
+          <t>Se usa «Isoval — Arquitectura &amp; Construcción» y @isoval.arq. Ojo: el sitio y el logo del repositorio (index.html, imgs/logo.png) están a nombre de LAB A+A y con otra paleta. Si la cuenta de Instagram ya opera como LAB A+A, cambia el nombre en los copys.</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E8192C"/>
+    <tabColor rgb="002B7D89"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2128,7 +2128,7 @@
           <t>REUTILIZAR el carrusel «5 Pasos» que ya existe. Solo actualizar:
 • Lámina 1 (portada): nuevo titular «De la idea a la llave en mano»
 • Lámina 6 (cierre): CTA con el WhatsApp 311 161 4155
-• Revisar que los colores sigan la paleta (crema #F3EDE0, carbón #231C10, rojo #E8192C)
+• Revisar que los colores sigan la paleta (hueso #F5F3EE, ink #1B1E1F, teal #2B7D89)
 Las láminas 2–5 se quedan igual. Trabajo de 20 minutos.</t>
         </is>
       </c>
@@ -2206,11 +2206,11 @@
       <c r="L6" s="35" t="inlineStr">
         <is>
           <t>REEL sencillo. Guion visual:
-0–3 s: texto grande sobre fondo crema — «¿Cuánto cuesta construir en Tepic?»
+0–3 s: texto grande sobre fondo hueso — «¿Cuánto cuesta construir en Tepic?»
 3–15 s: b-roll de obra (celular sirve) con los rangos sobreimpresos
 15–28 s: plano de planos/renders + «el número real sale de TU terreno»
 28–35 s: cierre con logo y el WhatsApp
-Tipografía en carbón #231C10, subrayados en rojo #E8192C.</t>
+Tipografía en ink #1B1E1F, subrayados en teal #2B7D89.</t>
         </is>
       </c>
       <c r="M6" s="33" t="inlineStr">
@@ -2287,10 +2287,10 @@
       </c>
       <c r="L7" s="35" t="inlineStr">
         <is>
-          <t>Diseño simple sobre fondo crema #F3EDE0:
-• Titular grande en carbón: «Consulta inicial\nsin costo»
-• Los 4 bullets con palomita en rojo #E8192C
-• Franja inferior carbón con logo + WhatsApp 311 161 4155
+          <t>Diseño simple sobre fondo hueso #F5F3EE:
+• Titular grande en ink: «Consulta inicial / sin costo»
+• Los 4 bullets con palomita en teal #2B7D89
+• Franja inferior ink con logo + WhatsApp 311 161 4155
 Sin foto o con foto de fondo al 15% de opacidad.</t>
         </is>
       </c>
@@ -2369,8 +2369,8 @@
 • Lámina 1: DESPUÉS (la foto más fuerte)
 • Lámina 2: ANTES
 • Lámina 3: detalle del cambio (unión, luz, acabado)
-• Lámina 4 (opcional): CTA en fondo carbón
-Etiquetas «ANTES» / «DESPUÉS» en rojo #E8192C, esquina superior.</t>
+• Lámina 4 (opcional): CTA en fondo ink
+Etiquetas «ANTES» / «DESPUÉS» en teal #2B7D89, esquina superior.</t>
         </is>
       </c>
       <c r="M8" s="29" t="inlineStr">
@@ -2444,9 +2444,9 @@
       <c r="L9" s="32" t="inlineStr">
         <is>
           <t>Post de texto con jerarquía fuerte:
-• Fondo carbón #231C10
-• Titular en crema #F3EDE0: «Presupuesto\nejecutivo\ncerrado»
-• Debajo, en rojo #E8192C: «El costo se define antes, no después.»
+• Fondo ink #1B1E1F
+• Titular en hueso #F5F3EE: «Presupuesto / ejecutivo / cerrado»
+• Debajo, en teal #2B7D89: «El costo se define antes, no después.»
 • Logo abajo a la izquierda
 Cero foto. Este contrasta con el feed y frena el scroll.</t>
         </is>
@@ -2526,9 +2526,9 @@
       <c r="L10" s="32" t="inlineStr">
         <is>
           <t>Diseño tipo «agenda»:
-• Fondo crema #F3EDE0 con una cuadrícula sutil de calendario
-• Titular carbón: «Agenda de obra\nSeptiembre»
-• Sello diagonal en rojo #E8192C: «Cupo limitado»
+• Fondo hueso #F5F3EE con una cuadrícula sutil de calendario
+• Titular ink: «Agenda de obra / Septiembre»
+• Sello diagonal en teal #2B7D89: «Cupo limitado»
 • Franja inferior con WhatsApp 311 161 4155
 Escasez real: solo úsala si de verdad hay cupo limitado.</t>
         </is>
@@ -2604,8 +2604,8 @@
       </c>
       <c r="L11" s="35" t="inlineStr">
         <is>
-          <t>Preferido: FOTO REAL de entrega o del proyecto terminado, con la cita sobreimpresa en crema sobre una franja carbón semitransparente.
-Alternativa si no hay foto: post de cita — fondo crema, comillas grandes en rojo #E8192C, texto en carbón, crédito debajo («Familia R., Tepic» o similar).
+          <t>Preferido: FOTO REAL de entrega o del proyecto terminado, con la cita sobreimpresa en hueso sobre una franja ink semitransparente.
+Alternativa si no hay foto: post de cita — fondo hueso, comillas grandes en teal #2B7D89, texto en ink, crédito debajo («Familia R., Tepic» o similar).
 Pedir autorización al cliente antes de nombrarlo.</t>
         </is>
       </c>
@@ -2685,10 +2685,10 @@
       <c r="L12" s="35" t="inlineStr">
         <is>
           <t>Cierre fuerte, alta contraste:
-• Fondo carbón #231C10 a página completa
-• Titular en crema: «Última llamada\npara arrancar\neste año»
-• Los 4 bullets en crema con viñetas rojas #E8192C
-• Barra inferior roja con el WhatsApp en blanco
+• Fondo ink #1B1E1F a página completa
+• Titular en hueso: «Última llamada / para arrancar / este año»
+• Los 4 bullets en hueso con viñetas teal #2B7D89
+• Barra inferior teal con el WhatsApp en blanco
 Reutiliza la retícula del post #8 para mantener consistencia.</t>
         </is>
       </c>
@@ -2729,7 +2729,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E8192C"/>
+    <tabColor rgb="002B7D89"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>Captura del post #1, fondo crema, sticker de flecha apuntando al post.</t>
+          <t>Captura del post #1, fondo hueso, sticker de flecha apuntando al post.</t>
         </is>
       </c>
       <c r="F2" s="32" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>Dos fotos de material una encima de otra, palomita verde y tache rojo.</t>
+          <t>Dos fotos de material una encima de otra, palomita verde y tache teal.</t>
         </is>
       </c>
       <c r="F4" s="32" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>Fondo carbón, caja de preguntas centrada. Las respuestas se contestan en stories durante la semana — cada respuesta es contenido.</t>
+          <t>Fondo ink, caja de preguntas centrada. Las respuestas se contestan en stories durante la semana — cada respuesta es contenido.</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>3 stories de texto sobre fondo carbón, una señal por story, tipografía grande.</t>
+          <t>3 stories de texto sobre fondo ink, una señal por story, tipografía grande.</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Fondo crema con sello rojo «Cupo limitado» + los 3 datos que hay que mandar.</t>
+          <t>Fondo hueso con sello teal «Cupo limitado» + los 3 datos que hay que mandar.</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
